--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 3,34</t>
+          <t>-9,97; 2,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 10,2</t>
+          <t>-7,14; 10,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 19,24</t>
+          <t>1,24; 19,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 19,64</t>
+          <t>-4,03; 20,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 21,89</t>
+          <t>-43,62; 17,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 22,7</t>
+          <t>-13,42; 22,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 61,46</t>
+          <t>3,11; 61,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 218,55</t>
+          <t>-22,1; 227,75</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 11,03</t>
+          <t>-1,31; 11,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,87; 26,43</t>
+          <t>13,61; 26,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 16,48</t>
+          <t>2,08; 15,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 10,19</t>
+          <t>-18,4; 9,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 44,06</t>
+          <t>-3,82; 45,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,54; 51,49</t>
+          <t>22,77; 51,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 31,75</t>
+          <t>3,34; 29,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 42,95</t>
+          <t>-51,02; 40,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,43</t>
+          <t>-2,56; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,0</t>
+          <t>-0,44; 8,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,35</t>
+          <t>-2,1; 9,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 1,41</t>
+          <t>-14,24; 1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 35,75</t>
+          <t>-8,16; 34,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 13,2</t>
+          <t>-0,67; 12,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 16,29</t>
+          <t>-3,12; 16,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 4,19</t>
+          <t>-40,69; 4,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,79</t>
+          <t>-2,03; 8,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,59; -3,76</t>
+          <t>-16,85; -4,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,72</t>
+          <t>-6,8; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 2,59</t>
+          <t>-8,68; 2,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 66,4</t>
+          <t>-11,82; 64,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,66; -7,61</t>
+          <t>-29,02; -8,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 17,94</t>
+          <t>-15,58; 16,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 11,47</t>
+          <t>-31,17; 11,55</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,88</t>
+          <t>0,03; 11,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,62</t>
+          <t>-5,11; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 9,29</t>
+          <t>-4,79; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,35</t>
+          <t>-4,59; 5,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 99,46</t>
+          <t>-1,42; 103,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 37,76</t>
+          <t>-15,21; 35,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 44,85</t>
+          <t>-18,13; 45,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 34,01</t>
+          <t>-20,85; 33,46</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 14,75</t>
+          <t>3,49; 15,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 4,23</t>
+          <t>-11,3; 3,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 11,36</t>
+          <t>-2,0; 11,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 65,96</t>
+          <t>3,22; 65,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,07; 131,82</t>
+          <t>18,71; 137,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 16,82</t>
+          <t>-32,39; 14,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 58,86</t>
+          <t>-8,45; 61,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,16; 705,09</t>
+          <t>25,28; 744,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 12,25</t>
+          <t>-3,65; 11,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 11,77</t>
+          <t>-4,37; 13,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 20,17</t>
+          <t>4,45; 20,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,14; 19,55</t>
+          <t>7,65; 18,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 52,96</t>
+          <t>-10,49; 50,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 28,41</t>
+          <t>-8,49; 32,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 61,52</t>
+          <t>10,81; 62,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,28; 73,65</t>
+          <t>22,72; 69,52</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,7</t>
+          <t>1,95; 6,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,85</t>
+          <t>-0,45; 4,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,92</t>
+          <t>2,47; 7,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 23,77</t>
+          <t>1,97; 24,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 32,93</t>
+          <t>8,87; 31,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,61</t>
+          <t>-0,85; 9,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,56</t>
+          <t>5,59; 19,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,39; 103,65</t>
+          <t>8,46; 113,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 2,66</t>
+          <t>-9,26; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 10,34</t>
+          <t>-6,49; 9,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 19,02</t>
+          <t>0,61; 18,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 20,06</t>
+          <t>-5,08; 20,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 17,92</t>
+          <t>-41,66; 22,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 22,5</t>
+          <t>-11,87; 21,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 61,31</t>
+          <t>0,83; 58,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 227,75</t>
+          <t>-20,06; 161,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,77%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,64</t>
+          <t>-1,99; 10,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 26,65</t>
+          <t>14,22; 26,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 15,48</t>
+          <t>1,83; 16,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 9,81</t>
+          <t>-7,58; 12,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 45,32</t>
+          <t>-6,11; 41,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,77; 51,68</t>
+          <t>24,32; 50,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 29,67</t>
+          <t>3,01; 32,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 40,83</t>
+          <t>-20,16; 48,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-15,81%</t>
+          <t>-9,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 8,27</t>
+          <t>-2,34; 8,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,97</t>
+          <t>-1,61; 8,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,59</t>
+          <t>-1,82; 9,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 1,33</t>
+          <t>-8,65; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 34,07</t>
+          <t>-8,26; 35,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 12,86</t>
+          <t>-2,14; 12,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 16,57</t>
+          <t>-2,78; 17,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 4,49</t>
+          <t>-23,72; 9,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-10,26%</t>
+          <t>-3,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,44</t>
+          <t>-2,34; 8,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -4,35</t>
+          <t>-16,93; -3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 6,14</t>
+          <t>-7,73; 5,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 2,52</t>
+          <t>-5,48; 3,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 64,71</t>
+          <t>-12,48; 65,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,02; -8,3</t>
+          <t>-28,86; -6,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 16,5</t>
+          <t>-17,45; 14,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 11,55</t>
+          <t>-19,89; 16,12</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 11,9</t>
+          <t>0,44; 11,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,57</t>
+          <t>-4,89; 8,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 9,13</t>
+          <t>-4,04; 9,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 5,34</t>
+          <t>-5,45; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 103,95</t>
+          <t>2,12; 99,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 35,95</t>
+          <t>-14,86; 32,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 45,26</t>
+          <t>-14,81; 48,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 33,46</t>
+          <t>-23,47; 31,18</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32,79</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>281,76%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 15,33</t>
+          <t>3,85; 15,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 3,68</t>
+          <t>-10,17; 4,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 11,73</t>
+          <t>-1,75; 11,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 65,97</t>
+          <t>1,54; 8,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,71; 137,47</t>
+          <t>21,7; 135,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 14,09</t>
+          <t>-31,06; 16,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 61,47</t>
+          <t>-7,29; 62,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,28; 744,0</t>
+          <t>12,28; 88,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 11,95</t>
+          <t>-4,48; 11,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 13,43</t>
+          <t>-5,82; 11,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 20,2</t>
+          <t>3,25; 19,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 18,4</t>
+          <t>8,16; 19,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 50,77</t>
+          <t>-13,31; 49,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 32,36</t>
+          <t>-10,99; 29,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,81; 62,28</t>
+          <t>8,04; 60,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,72; 69,52</t>
+          <t>24,62; 74,22</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,62</t>
+          <t>2,08; 6,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,92</t>
+          <t>-0,35; 5,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,85</t>
+          <t>2,85; 8,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 24,73</t>
+          <t>1,19; 5,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,87; 31,64</t>
+          <t>8,81; 32,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,75</t>
+          <t>-0,67; 9,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 19,51</t>
+          <t>6,59; 20,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 113,11</t>
+          <t>4,49; 25,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
